--- a/MyFurionApi.Web.Entry/wwwroot/template/导出模板.xlsx
+++ b/MyFurionApi.Web.Entry/wwwroot/template/导出模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GitHub\MyFurionApi\MyFurionApi.Web.Entry\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A4225F-C0DA-46D1-83A4-6D9496A88F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E7DAD2-6FA0-423F-803F-129B55F4ACB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,50 +31,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{RegionFull}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{CreatedTime}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合同编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{Table&gt;&gt;DataList|Code}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合同名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{Name}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合同类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CTypeName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>签订时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{SignDate}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{Value}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合同金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,11 +55,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{FlagName|&gt;&gt;Table}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.Code}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.Name}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.CTypeName}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.SignDate}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.Value}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.RegionFull}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.CreatedTime}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DataList.FlagName}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -487,54 +487,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
